--- a/releaf-six-minds-zh.xlsx
+++ b/releaf-six-minds-zh.xlsx
@@ -4350,7 +4350,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 法律允許、社群也接受的用途</t>
+          <t xml:space="preserve">一個設計決策 → 促成它的人，以及框住它的規則</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 法律允許、社群也接受的用途</t>
+          <t xml:space="preserve">一個設計決策 → 促成它的人，以及框住它的規則</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 法律允許、社群也接受的用途</t>
+          <t xml:space="preserve">一個設計決策 → 促成它的人，以及框住它的規則</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 法律允許、社群也接受的用途</t>
+          <t xml:space="preserve">一個設計決策 → 促成它的人，以及框住它的規則</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 法律允許、社群也接受的用途</t>
+          <t xml:space="preserve">一個設計決策 → 促成它的人，以及框住它的規則</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 法律允許、社群也接受的用途</t>
+          <t xml:space="preserve">一個設計決策 → 促成它的人，以及框住它的規則</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 法律允許、社群也接受的用途</t>
+          <t xml:space="preserve">一個設計決策 → 促成它的人，以及框住它的規則</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 法律允許、社群也接受的用途</t>
+          <t xml:space="preserve">一個設計決策 → 促成它的人，以及框住它的規則</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 法律允許、社群也接受的用途</t>
+          <t xml:space="preserve">一個設計決策 → 促成它的人，以及框住它的規則</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 法律允許、社群也接受的用途</t>
+          <t xml:space="preserve">一個設計決策 → 促成它的人，以及框住它的規則</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4783,27 +4783,27 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">生物刺激素路徑所需試驗</t>
+          <t xml:space="preserve">白名單合規</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">由指定檢驗單位出具的肥料規格檢驗報告，加上支持宣稱效果的非生物逆境效力數據。值得注意的是，不需要動物毒理，也不需要跨季田間試驗。</t>
+          <t xml:space="preserve">高中隊伍必須在 iGEM 白名單內作業：不能用 BSL-2 生物、不能用動物、不能用人體檢體、不能用產孢真菌。其他腦袋提出的每一個菌株、零件與試驗，排程前都要先過這條線；這也是為什麼枯草桿菌 168 與阿拉伯芥其實從來不是真正開放的選項。</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">商業計畫 §6.2.1</t>
+          <t xml:space="preserve">iGEM 白名單</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">你宣稱它能做什麼</t>
+          <t xml:space="preserve">圍阻證據</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 HP2 HP3</t>
+          <t xml:space="preserve">P5 HP3 P2</t>
         </is>
       </c>
     </row>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 法律允許、社群也接受的用途</t>
+          <t xml:space="preserve">一個設計決策 → 促成它的人，以及框住它的規則</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4830,27 +4830,27 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">避開的生物農藥試驗組合</t>
+          <t xml:space="preserve">安全表單與風險登錄</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">GLP 急毒性（口服、皮膚、吸入）；眼與皮膚刺激性；水生生物與非標的昆蟲測試；以及官方跨季效力與藥害田間試驗。只要不宣稱病害防治，就能避開這些年份與重資本。</t>
+          <t xml:space="preserve">已送出的專案安全表單，以及背後的風險登錄：膜通透性、藥害、AND 閘可靠度、三道防線各自的圍阻失效。評審可以在團隊儀表板上看到審查後的表單，所以它必須和台上講的一致。</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">商業計畫 §6.2.1</t>
+          <t xml:space="preserve">安全表單 × §6.1</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">你宣稱它能做什麼</t>
+          <t xml:space="preserve">圍阻證據</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 HP2 HP3</t>
+          <t xml:space="preserve">P5 HP3 P8</t>
         </is>
       </c>
     </row>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 法律允許、社群也接受的用途</t>
+          <t xml:space="preserve">一個設計決策 → 促成它的人，以及框住它的規則</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4877,27 +4877,27 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">給主管機關的圍阻證據</t>
+          <t xml:space="preserve">生物刺激素路徑所需試驗</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">主管機關要接受「封閉使用」需要什麼，這個標準比二十分鐘內說服評審更高，也不一樣。</t>
+          <t xml:space="preserve">由指定檢驗單位出具的肥料規格檢驗報告，加上支持宣稱效果的非生物逆境效力數據。值得注意的是，不需要動物毒理，也不需要跨季田間試驗。</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">商業計畫 §6.2</t>
+          <t xml:space="preserve">商業計畫 §6.2.1</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">圍阻證據</t>
+          <t xml:space="preserve">你宣稱它能做什麼</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">HP3 P3</t>
+          <t xml:space="preserve">P3 HP2 HP3</t>
         </is>
       </c>
     </row>
@@ -4914,37 +4914,37 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 法律允許、社群也接受的用途</t>
+          <t xml:space="preserve">一個設計決策 → 促成它的人，以及框住它的規則</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">乾實驗</t>
+          <t xml:space="preserve">濕實驗</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">農地面積對氣候波動</t>
+          <t xml:space="preserve">避開的生物農藥試驗組合</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">以地籍層級的農地面積資料，疊上由全國氣象站紀錄內插而成的氣候波動曲面，找出最小的農地與最難預測的氣候相遇的地方。</t>
+          <t xml:space="preserve">GLP 急毒性（口服、皮膚、吸入）；眼與皮膚刺激性；水生生物與非標的昆蟲測試；以及官方跨季效力與藥害田間試驗。只要不宣稱病害防治，就能避開這些年份與重資本。</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">地理空間分析</t>
+          <t xml:space="preserve">商業計畫 §6.2.1</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">把地圖變成數字</t>
+          <t xml:space="preserve">你宣稱它能做什麼</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1 P3 HP2 HP6 HP5</t>
+          <t xml:space="preserve">P3 HP2 HP3</t>
         </is>
       </c>
     </row>
@@ -4961,37 +4961,37 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 法律允許、社群也接受的用途</t>
+          <t xml:space="preserve">一個設計決策 → 促成它的人，以及框住它的規則</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">乾實驗</t>
+          <t xml:space="preserve">濕實驗</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">內插方法與不確定度</t>
+          <t xml:space="preserve">給主管機關的圍阻證據</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">使用的方法、背後的測站密度，以及你願意公開講的不確定度。模型組評審這三樣都會問。</t>
+          <t xml:space="preserve">主管機關要接受「封閉使用」需要什麼，這個標準比二十分鐘內說服評審更高，也不一樣。</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">地理空間分析</t>
+          <t xml:space="preserve">商業計畫 §6.2</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">把地圖變成數字</t>
+          <t xml:space="preserve">圍阻證據</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">P8 HP2 MS2 HP5</t>
+          <t xml:space="preserve">HP3 P3</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 法律允許、社群也接受的用途</t>
+          <t xml:space="preserve">一個設計決策 → 促成它的人，以及框住它的規則</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5018,27 +5018,27 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">肥料管理法對農藥管理法</t>
+          <t xml:space="preserve">農地面積對氣候波動</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">非生物逆境走肥料管理法，主管機關為農糧署。生物逆境走農藥管理法，主管機關為動植物防疫檢疫署（原防檢局）。宣稱決定適用哪一部法。</t>
+          <t xml:space="preserve">以地籍層級的農地面積資料，疊上由全國氣象站紀錄內插而成的氣候波動曲面，找出最小的農地與最難預測的氣候相遇的地方。</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">商業計畫 §6.2.1</t>
+          <t xml:space="preserve">地理空間分析</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">你宣稱它能做什麼</t>
+          <t xml:space="preserve">把地圖變成數字</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 HP2 HP3</t>
+          <t xml:space="preserve">P1 P3 HP2 HP6 HP5</t>
         </is>
       </c>
     </row>
@@ -5055,7 +5055,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 法律允許、社群也接受的用途</t>
+          <t xml:space="preserve">一個設計決策 → 促成它的人，以及框住它的規則</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5065,27 +5065,27 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">30 天對數年</t>
+          <t xml:space="preserve">內插方法與不確定度</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">肥料登記：規格檢驗報告約 20 天，加上約 7 天審查，合計約 30 天。微生物農藥登記則要好幾年。</t>
+          <t xml:space="preserve">使用的方法、背後的測站密度，以及你願意公開講的不確定度。模型組評審這三樣都會問。</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">商業計畫 §6.2.1</t>
+          <t xml:space="preserve">地理空間分析</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">你宣稱它能做什麼</t>
+          <t xml:space="preserve">把地圖變成數字</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 HP2</t>
+          <t xml:space="preserve">P8 HP2 MS2 HP5</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 法律允許、社群也接受的用途</t>
+          <t xml:space="preserve">一個設計決策 → 促成它的人，以及框住它的規則</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5112,27 +5112,27 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">封閉使用對環境釋出</t>
+          <t xml:space="preserve">肥料管理法對農藥管理法</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">改造枯草桿菌全程封閉，只排出非活體代謝產物，這是主張不落入基改環境釋出架構的論證。圍阻必須向主管機關證明，不能只是聲稱。</t>
+          <t xml:space="preserve">非生物逆境走肥料管理法，主管機關為農糧署。生物逆境走農藥管理法，主管機關為動植物防疫檢疫署（原防檢局）。宣稱決定適用哪一部法。</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">商業計畫 §6.2</t>
+          <t xml:space="preserve">商業計畫 §6.2.1</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">圍阻證據</t>
+          <t xml:space="preserve">你宣稱它能做什麼</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">HP3 P3</t>
+          <t xml:space="preserve">P3 HP2 HP3</t>
         </is>
       </c>
     </row>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 法律允許、社群也接受的用途</t>
+          <t xml:space="preserve">一個設計決策 → 促成它的人，以及框住它的規則</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5159,27 +5159,27 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">歸屬：學生與外部協助的分界</t>
+          <t xml:space="preserve">30 天對數年</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">貢獻歸屬表必須把專案構想、設計、執行分開列出，並具名說明每位協助者做了什麼。評審會檢查是否每個欄位（含具體任務）都填了，以及是否與團隊的實際成果相符。</t>
+          <t xml:space="preserve">肥料登記：規格檢驗報告約 20 天，加上約 7 天審查，合計約 30 天。微生物農藥登記則要好幾年。</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">評審手冊 p.25</t>
+          <t xml:space="preserve">商業計畫 §6.2.1</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">你宣稱它能做什麼</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">P6 P8</t>
+          <t xml:space="preserve">P3 HP2</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 法律允許、社群也接受的用途</t>
+          <t xml:space="preserve">一個設計決策 → 促成它的人，以及框住它的規則</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5206,27 +5206,27 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">每個獎項一個標準頁面</t>
+          <t xml:space="preserve">封閉使用對環境釋出</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">每一項獎牌條件與每一個特殊獎項都有固定的 wiki 網址。評審由選票直接連過去，沒有義務到別處找；放在 iGEM 伺服器以外的內容完全不能被評分。</t>
+          <t xml:space="preserve">改造枯草桿菌全程封閉，只排出非活體代謝產物，這是主張不落入基改環境釋出架構的論證。圍阻必須向主管機關證明，不能只是聲稱。</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">評審手冊 p.29</t>
+          <t xml:space="preserve">商業計畫 §6.2</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">圍阻證據</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">P8 HP5</t>
+          <t xml:space="preserve">HP3 P3</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 法律允許、社群也接受的用途</t>
+          <t xml:space="preserve">一個設計決策 → 促成它的人，以及框住它的規則</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5253,64 +5253,64 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">向防檢署取得書面意見</t>
+          <t xml:space="preserve">對話與改動對照表</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">在任何田間或溫室部署前先取得書面意見，因為主管機關仍可能把改造細菌分泌的化合物歸類為需要基改核准。在釐清之前，所有測試都維持在封閉的實驗室內。</t>
+          <t xml:space="preserve">一張表：每一場對話、它改變的設計決策、以及隨後跑的實驗。鄭梅君讓試驗改用洋菜，Brophy 把圍阻移進硬體，黃介辰把釋放提到逆境之前，Verslue 改變了我們要分泌什麼。沒有這張表，這些只是軼事；有了它，才是整合式人本實踐。</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">商業計畫 §6.1</t>
+          <t xml:space="preserve">全部利害關係人紀錄</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">圍阻證據 · 你宣稱它能做什麼</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">HP3 P3 HP2</t>
+          <t xml:space="preserve">HP1 HP2 HP5 P5</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">M6</t>
+          <t xml:space="preserve">M5</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">商業模式與創業</t>
+          <t xml:space="preserve">人本實踐與法規</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 有定價、有買家、有毛利的產品</t>
+          <t xml:space="preserve">一個設計決策 → 促成它的人，以及框住它的規則</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">人本實踐</t>
+          <t xml:space="preserve">乾實驗</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">陳文亮 · 印表機與墨水</t>
+          <t xml:space="preserve">這個設計排除了誰</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">商業模式參照便宜機器、昂貴耗材。先確認誰付錢，而不是誰使用。B2C 很難做，需要諮詢與信任。不要在價格上跟便宜的化學肥料硬碰，並考慮先做國外市場再回頭擴張本地。</t>
+          <t xml:space="preserve">封閉裝置加卡匣訂閱，會排除負擔不起經常性支出的農民；單鍵介面之所以存在，是因為黃介辰與陳惠雯都描述過高齡的農村使用者。點名這個設計觸及不到的人，以及要觸及他們必須改變什麼。</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/10 AgriTalk</t>
+          <t xml:space="preserve">黃介辰、陳惠雯</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5320,91 +5320,91 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 P5 HP1</t>
+          <t xml:space="preserve">HP3 HP4 HP6 P5</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">M6</t>
+          <t xml:space="preserve">M5</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">商業模式與創業</t>
+          <t xml:space="preserve">人本實踐與法規</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 有定價、有買家、有毛利的產品</t>
+          <t xml:space="preserve">一個設計決策 → 促成它的人，以及框住它的規則</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">人本實踐</t>
+          <t xml:space="preserve">乾實驗</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">正瀚 · 定位與法規</t>
+          <t xml:space="preserve">公共論壇與農漁週</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">在台灣，熱與乾旱的市場需求最大。法規要在設計實驗之前考慮，不是之後。面對化學農藥的定位，以及台灣由哪些農場執行田間試驗。</t>
+          <t xml:space="preserve">9/5 公共論壇與 9/9 農漁週。綠媒體把討論時間從 10 分鐘拉到 30 分鐘，並建議邀請會買醜蔬果的人來談，論壇因此改版。是雙向活動，不是簡報。</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">7/9 正瀚生技</t>
+          <t xml:space="preserve">7/7 綠媒體</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">你宣稱它能做什麼</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 P5 HP1 HP2</t>
+          <t xml:space="preserve">HP4 HP5 HP6 P5</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">M6</t>
+          <t xml:space="preserve">M5</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">商業模式與創業</t>
+          <t xml:space="preserve">人本實踐與法規</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 有定價、有買家、有毛利的產品</t>
+          <t xml:space="preserve">一個設計決策 → 促成它的人，以及框住它的規則</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">人本實踐</t>
+          <t xml:space="preserve">乾實驗</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">源鮮 · 兩種客層</t>
+          <t xml:space="preserve">歸屬：學生與外部協助的分界</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">小農要的是主食作物的逆境保護。大型企業要的是生長速度，以及香辛料、生菜等高價作物的保護。一個產品，兩套價值主張。</t>
+          <t xml:space="preserve">貢獻歸屬表必須把專案構想、設計、執行分開列出，並具名說明每位協助者做了什麼。評審會檢查是否每個欄位（含具體任務）都填了，以及是否與團隊的實際成果相符。</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/11 源鮮智慧農場</t>
+          <t xml:space="preserve">評審手冊 p.25</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5414,101 +5414,101 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 P5 HP1 HP4</t>
+          <t xml:space="preserve">P6 P8</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">M6</t>
+          <t xml:space="preserve">M5</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">商業模式與創業</t>
+          <t xml:space="preserve">人本實踐與法規</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 有定價、有買家、有毛利的產品</t>
+          <t xml:space="preserve">一個設計決策 → 促成它的人，以及框住它的規則</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">人本實踐</t>
+          <t xml:space="preserve">乾實驗</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">生技展 · 標題數字</t>
+          <t xml:space="preserve">每個獎項一個標準頁面</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">競爭對手的攤位都錨定在一兩個數字上，通常是產量或排放，而審查者也會把那些數字複述回來。挑出這個專案要被記住的一到三個數字，讓它們出現在每個地方，而不是描述機制、期待別人自己推算。</t>
+          <t xml:space="preserve">每一項獎牌條件與每一個特殊獎項都有固定的 wiki 網址。評審由選票直接連過去，沒有義務到別處找；放在 iGEM 伺服器以外的內容完全不能被評分。</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">7/18 南港展覽館</t>
+          <t xml:space="preserve">評審手冊 p.29</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">機器與卡匣</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1 P3 P5 HP1</t>
+          <t xml:space="preserve">P8 HP5</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">M6</t>
+          <t xml:space="preserve">M5</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">商業模式與創業</t>
+          <t xml:space="preserve">人本實踐與法規</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 有定價、有買家、有毛利的產品</t>
+          <t xml:space="preserve">一個設計決策 → 促成它的人，以及框住它的規則</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">濕實驗</t>
+          <t xml:space="preserve">乾實驗</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">每次卡匣運轉的產量</t>
+          <t xml:space="preserve">向防檢署取得書面意見</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">一個卡匣在其生命週期內能產出多少保護劑，以毫克計。這是拿去賣的單位；在這個數字出現之前，定價只是猜測。</t>
+          <t xml:space="preserve">在任何田間或溫室部署前先取得書面意見，因為主管機關仍可能把改造細菌分泌的化合物歸類為需要基改核准。在釐清之前，所有測試都維持在封閉的實驗室內。</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">M4 反應器運轉</t>
+          <t xml:space="preserve">商業計畫 §6.1</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">機器與卡匣</t>
+          <t xml:space="preserve">圍阻證據 · 你宣稱它能做什麼</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2 P3 MS4</t>
+          <t xml:space="preserve">HP3 P3 HP2</t>
         </is>
       </c>
     </row>
@@ -5525,37 +5525,37 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 有定價、有買家、有毛利的產品</t>
+          <t xml:space="preserve">我們自己的數據 → 規格下限、單位成本、市場規模、影響數字</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">濕實驗</t>
+          <t xml:space="preserve">人本實踐</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">負載下的卡匣壽命</t>
+          <t xml:space="preserve">陳文亮 · 印表機與墨水</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">在產出降到有效劑量以下之前，能連續運轉幾天。更換週期就是收入的節奏，因此這個實驗決定經常性收入的程度，不亞於它決定維護頻率。</t>
+          <t xml:space="preserve">商業模式參照便宜機器、昂貴耗材。先確認誰付錢，而不是誰使用。B2C 很難做，需要諮詢與信任。不要在價格上跟便宜的化學肥料硬碰，並考慮先做國外市場再回頭擴張本地。</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">M4 × 商業計畫</t>
+          <t xml:space="preserve">4/10 AgriTalk</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">機器與卡匣 · 代謝負擔</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 HW3 P2</t>
+          <t xml:space="preserve">P3 P5 HP1</t>
         </is>
       </c>
     </row>
@@ -5572,37 +5572,37 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 有定價、有買家、有毛利的產品</t>
+          <t xml:space="preserve">我們自己的數據 → 規格下限、單位成本、市場規模、影響數字</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">濕實驗</t>
+          <t xml:space="preserve">人本實踐</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">菌株保存穩定性</t>
+          <t xml:space="preserve">正瀚 · 定位與法規</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">卡匣在常溫下能否撐過儲存與運輸，以及能撐多久。需要冷鏈的耗材，成本結構完全不同，市場也小得多。</t>
+          <t xml:space="preserve">在台灣，熱與乾旱的市場需求最大。法規要在設計實驗之前考慮，不是之後。面對化學農藥的定位，以及台灣由哪些農場執行田間試驗。</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">正瀚 × 濕實驗</t>
+          <t xml:space="preserve">7/9 正瀚生技</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">機器與卡匣</t>
+          <t xml:space="preserve">你宣稱它能做什麼</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 P2</t>
+          <t xml:space="preserve">P3 P5 HP1 HP2</t>
         </is>
       </c>
     </row>
@@ -5619,37 +5619,37 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 有定價、有買家、有毛利的產品</t>
+          <t xml:space="preserve">我們自己的數據 → 規格下限、單位成本、市場規模、影響數字</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">乾實驗</t>
+          <t xml:space="preserve">人本實踐</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">從地圖到可服務市場</t>
+          <t xml:space="preserve">源鮮 · 兩種客層</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">把交會曲面換成可以計數的東西：高重疊區內的公頃數、其中一公頃以下的農戶數，以及在第二階段密度下代表多少台裝置。這一步讓地理分析在商業計畫裡真正發揮作用。</t>
+          <t xml:space="preserve">小農要的是主食作物的逆境保護。大型企業要的是生長速度，以及香辛料、生菜等高價作物的保護。一個產品，兩套價值主張。</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">地理分析 × 商業計畫</t>
+          <t xml:space="preserve">8/11 源鮮智慧農場</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">把地圖變成數字 · 機器與卡匣</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1 P3 HP2 HP6</t>
+          <t xml:space="preserve">P3 P5 HP1 HP4</t>
         </is>
       </c>
     </row>
@@ -5666,27 +5666,27 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 有定價、有買家、有毛利的產品</t>
+          <t xml:space="preserve">我們自己的數據 → 規格下限、單位成本、市場規模、影響數字</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">乾實驗</t>
+          <t xml:space="preserve">人本實踐</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">機器便宜、卡匣持續</t>
+          <t xml:space="preserve">生技展 · 標題數字</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">反應器的製造成本決定硬體售價，卡匣更換週期決定收入節奏。兩個數字都來自 M4，因此沒有硬體組在場，商業模式寫不出來。</t>
+          <t xml:space="preserve">競爭對手的攤位都錨定在一兩個數字上，通常是產量或排放，而審查者也會把那些數字複述回來。挑出這個專案要被記住的一到三個數字，讓它們出現在每個地方，而不是描述機制、期待別人自己推算。</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">陳文亮 × 硬體</t>
+          <t xml:space="preserve">7/18 南港展覽館</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 HP1 P1</t>
+          <t xml:space="preserve">P1 P3 P5 HP1</t>
         </is>
       </c>
     </row>
@@ -5713,37 +5713,37 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 有定價、有買家、有毛利的產品</t>
+          <t xml:space="preserve">我們自己的數據 → 規格下限、單位成本、市場規模、影響數字</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">乾實驗</t>
+          <t xml:space="preserve">濕實驗</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">市場順序及其理由</t>
+          <t xml:space="preserve">LPA 劑量反應曲線</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">首站菲律賓，依 NCBP 封閉使用指引。次站越南，依 43/2026/ND-CP 號法令，加上湄公河鹽化問題。台灣做封閉驗證。歐盟因預防原則只列為長期。</t>
+          <t xml:space="preserve">我們在光板裝置上自己量到的光強度對保護劑產出關係。計畫的第一條線從這裡開始：沒有這條曲線，「開關可控」就只是一句話。</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">商業計畫 §6.2</t>
+          <t xml:space="preserve">M1 × LPA</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">光劑量 · 機器與卡匣</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 HP2</t>
+          <t xml:space="preserve">P1 P2 MS4 P3</t>
         </is>
       </c>
     </row>
@@ -5760,37 +5760,37 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 有定價、有買家、有毛利的產品</t>
+          <t xml:space="preserve">我們自己的數據 → 規格下限、單位成本、市場規模、影響數字</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">乾實驗</t>
+          <t xml:space="preserve">濕實驗</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">專利對營業秘密</t>
+          <t xml:space="preserve">對照下的植物挽救</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">AND 閘迴路設計、CFMDI 膜設計、雙模組架構走專利。啟動子序列與訊號胜肽組合留作營業秘密。要注意這與 iGEM 公開發表要求之間的張力。</t>
+          <t xml:space="preserve">鹽逆境挽救，對照未處理植株、純培養基、未改造菌株流出液、不含保護劑的反應器流出液。這是整份計畫裡唯一能證明產品確實改變植物的證據。</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">商業計畫 §6.2</t>
+          <t xml:space="preserve">M1 植物試驗</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">對照與校正 · 機器與卡匣</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 HP3</t>
+          <t xml:space="preserve">P1 P2 MS4 P3</t>
         </is>
       </c>
     </row>
@@ -5807,27 +5807,27 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 有定價、有買家、有毛利的產品</t>
+          <t xml:space="preserve">我們自己的數據 → 規格下限、單位成本、市場規模、影響數字</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">乾實驗</t>
+          <t xml:space="preserve">濕實驗</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">卡匣成本對一季殺菌劑</t>
+          <t xml:space="preserve">每卡匣產量</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">一季的卡匣費用不能高於農民目前一季的殺菌劑支出。財務模型對成本與售價各做正負 20% 的敏感度分析。</t>
+          <t xml:space="preserve">一個卡匣在其生命週期內能產出多少保護劑，以毫克計。這是拿去賣的單位；在這個數字出現之前，定價只是猜測。</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">商業計畫 §6.1</t>
+          <t xml:space="preserve">M4 反應器運轉</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 HP3</t>
+          <t xml:space="preserve">P2 P3 MS4</t>
         </is>
       </c>
     </row>
@@ -5854,37 +5854,37 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 有定價、有買家、有毛利的產品</t>
+          <t xml:space="preserve">我們自己的數據 → 規格下限、單位成本、市場規模、影響數字</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">乾實驗</t>
+          <t xml:space="preserve">濕實驗</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">試點成功指標</t>
+          <t xml:space="preserve">卡匣壽命</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">每季殺菌劑施用次數減少 20 至 30%，氣候逆境下作物損失減少 10 至 15%，涵蓋 20 至 50 台裝置、20 至 70 位農民。要把這些講成目標，不是結果。</t>
+          <t xml:space="preserve">在產出降到規格下限以下之前，能連續運轉幾天。更換週期就是收入的節奏，因此這個實驗決定經常性收入的程度，不亞於它決定維護頻率。</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">商業計畫 §3.4</t>
+          <t xml:space="preserve">M4 × 商業計畫</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">機器與卡匣 · 代謝負擔</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 HP2 HP3</t>
+          <t xml:space="preserve">P3 HW3 P2</t>
         </is>
       </c>
     </row>
@@ -5901,27 +5901,27 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 有定價、有買家、有毛利的產品</t>
+          <t xml:space="preserve">我們自己的數據 → 規格下限、單位成本、市場規模、影響數字</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">乾實驗</t>
+          <t xml:space="preserve">濕實驗</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">部署擴張路徑</t>
+          <t xml:space="preserve">菌株保存穩定性</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">先 20 至 50 台試點、觸及 20 至 70 位農民，再擴到合作社的 150 至 400 台，最後在兩到三個國家達到 500 至 1500 台。方案 A 是硬體加卡匣，方案 B 是硬體加 API 與通用培養基。</t>
+          <t xml:space="preserve">卡匣在常溫下能否撐過儲存與運輸，以及能撐多久。需要冷鏈的耗材，成本結構完全不同，市場也小得多。</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">商業計畫 §3.4</t>
+          <t xml:space="preserve">正瀚 × 濕實驗</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 P1</t>
+          <t xml:space="preserve">P3 P2</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 有定價、有買家、有毛利的產品</t>
+          <t xml:space="preserve">我們自己的數據 → 規格下限、單位成本、市場規模、影響數字</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -5958,22 +5958,22 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">每台每季的價值</t>
+          <t xml:space="preserve">最低有效活性</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">模型從逆境頻率走到保護劑劑量、再走到植物效益。把效益乘上作物價格，就得到一台裝置在一季內對一位農民的價值，那就是任何人願意付的上限。</t>
+          <t xml:space="preserve">模型把植物讀值往回推，找出仍能產生可量測挽救效果的最低酵素活性。這個數字就是產品規格。計畫的第二條線就是它，沒有別的。</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">模型 × 商業計畫</t>
+          <t xml:space="preserve">M2 模型 × M1 試驗</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">機器與卡匣 · 把地圖變成數字</t>
+          <t xml:space="preserve">機器與卡匣 · 觸發閾值</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 有定價、有買家、有毛利的產品</t>
+          <t xml:space="preserve">我們自己的數據 → 規格下限、單位成本、市場規模、影響數字</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6005,27 +6005,27 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">每卡匣製造成本</t>
+          <t xml:space="preserve">規格下限到成本結構</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">培養基、菌株生產、膜卡匣與充填。對上 M4 給的反應器製造成本，這一組數字決定印表機與墨水模式成不成立。</t>
+          <t xml:space="preserve">下限決定一次運轉必須達到的效價，效價決定發酵體積、培養基消耗與卡匣尺寸，這些決定物料清單。下限一改，底下每一項成本都跟著動。</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">物料清單 × 發酵</t>
+          <t xml:space="preserve">M2 × M4</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">機器與卡匣</t>
+          <t xml:space="preserve">機器與卡匣 · 代謝負擔</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 HW4 P6</t>
+          <t xml:space="preserve">P3 P4 HW4</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 有定價、有買家、有毛利的產品</t>
+          <t xml:space="preserve">我們自己的數據 → 規格下限、單位成本、市場規模、影響數字</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6052,17 +6052,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">毛利與價格下限</t>
+          <t xml:space="preserve">每卡匣成本</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">卡匣成本對卡匣售價得出毛利；農民目前一季的殺菌劑支出則是天花板。若兩者之間沒有空間，該換的是付款方，不是價格。</t>
+          <t xml:space="preserve">膜、培養基、菌株生產、卡匣外殼與充填，全部按我們現有的機器估算，而不是照供應商型錄。第三條線從這裡開始。</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">商業計畫 §6.1、§7.1</t>
+          <t xml:space="preserve">M4 物料清單</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 P1</t>
+          <t xml:space="preserve">P3 HW4 P6</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 有定價、有買家、有毛利的產品</t>
+          <t xml:space="preserve">我們自己的數據 → 規格下限、單位成本、市場規模、影響數字</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6099,27 +6099,27 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">模組化卡匣即平台</t>
+          <t xml:space="preserve">耗電與運轉成本</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">同一個機體，可抽換的表現卡匣。選殖設計正是「第二種保護劑不需要第二家公司」的原因，也是方案 B 在賣的東西：硬體加 API，讓客戶培養自己在地分離的菌株。</t>
+          <t xml:space="preserve">LED 陣列、循環幫浦與控制器的實測瓦數，依 M1 給的工作週期換算成每季度電。黃介辰說過農民在意電費，所以這是拿來賣的數字，不是註腳。</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">M3 × 商業計畫</t>
+          <t xml:space="preserve">M4 × 黃介辰</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">一個機體、多種產品</t>
+          <t xml:space="preserve">機器與卡匣</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1 P3 P7</t>
+          <t xml:space="preserve">P3 HW3 HP1</t>
         </is>
       </c>
     </row>
@@ -6136,7 +6136,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 有定價、有買家、有毛利的產品</t>
+          <t xml:space="preserve">我們自己的數據 → 規格下限、單位成本、市場規模、影響數字</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6146,27 +6146,27 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">零件的實施自由</t>
+          <t xml:space="preserve">更換週期</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">CcaS-CcaR 系統、MoClo 標準與穿梭骨架都有來源。在任何申請之前，先釐清哪些有權利負擔、哪些已授權商業使用、哪些真的是我們可以主張的。</t>
+          <t xml:space="preserve">膜的壽命、卡匣更換間隔，以及多久要有人去看一次機器。乘上機隊規模，就得到每台每年的耗材需求，那就是整條經常性收入。</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">M3 × 法務</t>
+          <t xml:space="preserve">M4 × 商業計畫</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">一個機體、多種產品 · 你宣稱它能做什麼</t>
+          <t xml:space="preserve">機器與卡匣</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 P7 P8</t>
+          <t xml:space="preserve">P3 HW3</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 有定價、有買家、有毛利的產品</t>
+          <t xml:space="preserve">我們自己的數據 → 規格下限、單位成本、市場規模、影響數字</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6193,17 +6193,17 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">募資階段與所需證據</t>
+          <t xml:space="preserve">毛利與價格下限</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">三個階段各有不同的舉證責任：到 Jamboree 靠表現與分泌數據，Jamboree 後靠作物試驗與成本可行性，首次試點靠田間數據與法規路徑。說清楚每一類出資者要看到什麼，比說出金額更有說服力。</t>
+          <t xml:space="preserve">卡匣成本對卡匣售價得出毛利。若空間太薄，該換的是付款方，不是價格。</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">商業計畫 §7.2</t>
+          <t xml:space="preserve">商業計畫 §6.1、§7.1</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 HP2</t>
+          <t xml:space="preserve">P3 P1</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">可運作的裝置 → 有定價、有買家、有毛利的產品</t>
+          <t xml:space="preserve">我們自己的數據 → 規格下限、單位成本、市場規模、影響數字</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6240,25 +6240,495 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">競爭者與我們所在的空隙</t>
+          <t xml:space="preserve">台灣農民現在花多少</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">化學殺菌劑更便宜、現在就有效。CH Biotech 等商業生物刺激素可常溫保存、也已經在賣。兩者都無法在熱浪轉成病害爆發時即時調整，而那個空隙是唯一值得主張的位置。</t>
+          <t xml:space="preserve">每公頃每季的殺菌劑與肥料支出、背後的作物產值，以及 CH Biotech 的胜肽生物刺激素賣多少。我們價格的天花板是別人的發票，所以必須是真實數字。</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
+          <t xml:space="preserve">商業計畫 §4.3、§4.4</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">機器與卡匣</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3 P1 HP2</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M6</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">商業模式與創業</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">我們自己的數據 → 規格下限、單位成本、市場規模、影響數字</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">乾實驗</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每台每季價值</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M1 的挽救效果乘上作物價格，就是一台裝置對一位農民、一季的價值。那是任何人願意付的上限，而且它來自我們的試驗，不是論文。</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M1 × 模型</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">機器與卡匣 · 把地圖變成數字</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3 P4 P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M6</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">商業模式與創業</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">我們自己的數據 → 規格下限、單位成本、市場規模、影響數字</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">乾實驗</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">從地圖算出的可服務市場</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高重疊區內的公頃數、其中一公頃以下的農戶數，以及在第二階段密度下代表的裝置台數。第四條線從一個數字開始，不是一個形容詞。</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M5 地理分析</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">把地圖變成數字 · 機器與卡匣</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1 P3 HP2</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M6</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">商業模式與創業</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">我們自己的數據 → 規格下限、單位成本、市場規模、影響數字</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">乾實驗</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">量化的未來影響</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地圖描述的是現在的條件。把挽救數據與工作週期折進去，它就變成一句帶單位的陳述：在指定機隊規模下，保住多少公頃、留住多少公噸、少噴幾次。極少團隊做得出來，這正是它值得做的原因。</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M5 × M1 × 模型</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">把地圖變成數字 · 機器與卡匣</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1 P3 HP6 P4</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M6</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">商業模式與創業</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">我們自己的數據 → 規格下限、單位成本、市場規模、影響數字</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">乾實驗</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">法規成本與時程</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M5 的路徑研究對這門生意的代價：約 30 天加一份肥料規格檢驗報告，對上好幾年、GLP 動物毒理與跨季官方試驗。這個差距就是資本需求與首次收入的時間。</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M5 § 法規</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">你宣稱它能做什麼 · 機器與卡匣</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3 HP2 P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M6</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">商業模式與創業</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">我們自己的數據 → 規格下限、單位成本、市場規模、影響數字</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">乾實驗</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">擴張與市場順序</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">先 20 至 50 台試點，再到合作社的 150 至 400 台，最後在兩三個國家達到 500 至 1500 台。首站菲律賓依 NCBP 封閉使用指引，次站越南，台灣做封閉驗證。</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">商業計畫 §3.4、§6.2</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">機器與卡匣</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3 P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M6</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">商業模式與創業</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">我們自己的數據 → 規格下限、單位成本、市場規模、影響數字</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">乾實驗</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">試點指標對推估</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">目標是殺菌劑施用減少 20 至 30%、作物損失減少 10 至 15%。現在就把它們講成推估，再讓試點把每一項換成量測值。</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">商業計畫 §3.4</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">機器與卡匣</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3 HP2 HP3</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M6</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">商業模式與創業</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">我們自己的數據 → 規格下限、單位成本、市場規模、影響數字</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">乾實驗</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">智財：自有與借用</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AND 閘迴路、CFMDI 膜設計與雙模組架構走專利；啟動子序列與訊號胜肽組合留作營業秘密。任何申請之前，先查清楚 CcaS-CcaR、MoClo 與穿梭骨架各自帶著什麼權利負擔。</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M3 × 法務</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一個機體、多種產品 · 你宣稱它能做什麼</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3 P7 P8</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M6</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">商業模式與創業</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">我們自己的數據 → 規格下限、單位成本、市場規模、影響數字</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">乾實驗</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">卡匣即平台</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同一個機體，可抽換的表現卡匣。選殖設計正是「第二種保護劑只需要新卡匣、不需要新公司」的原因，也是方案 B 在賣的東西：硬體加 API，讓客戶培養自己在地的菌株。</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M3 × 商業計畫</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一個機體、多種產品</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1 P3 P7</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M6</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">商業模式與創業</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">我們自己的數據 → 規格下限、單位成本、市場規模、影響數字</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">乾實驗</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">募資階段</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">三個階段各有不同的舉證責任：到 Jamboree 靠表現與分泌數據，Jamboree 後靠作物試驗與成本可行性，首次試點靠田間數據與法規路徑。說清楚每一類出資者要看到什麼，勝過說出金額。</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">商業計畫 §7.2</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">機器與卡匣</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3 HP2</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M6</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">商業模式與創業</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">我們自己的數據 → 規格下限、單位成本、市場規模、影響數字</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">乾實驗</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">競爭者與空隙</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">化學殺菌劑更便宜、現在就有效。商業生物刺激素可常溫保存、也已經在賣。兩者都無法在熱浪轉成病害爆發時即時調整，而那個空隙是唯一值得主張的位置。</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
           <t xml:space="preserve">商業計畫 §4.3</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
+      <c r="H143" t="inlineStr">
         <is>
           <t xml:space="preserve">機器與卡匣</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
+      <c r="I143" t="inlineStr">
         <is>
           <t xml:space="preserve">P1 P3</t>
         </is>
@@ -6449,17 +6919,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
     </row>
@@ -6481,17 +6951,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
     </row>
@@ -6552,7 +7022,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
     </row>
@@ -6579,7 +7049,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
     </row>
@@ -6606,7 +7076,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
     </row>
@@ -6633,7 +7103,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
     </row>
@@ -6660,7 +7130,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
     </row>
@@ -6741,7 +7211,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
     </row>
@@ -6876,7 +7346,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
     </row>
@@ -6957,7 +7427,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
     </row>
@@ -6984,7 +7454,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
     </row>
@@ -7011,7 +7481,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7508,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7535,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
     </row>
@@ -7092,7 +7562,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
     </row>
@@ -7119,7 +7589,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7616,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
     </row>
